--- a/construction_template/data/templates_blank/estimate_report.xlsx
+++ b/construction_template/data/templates_blank/estimate_report.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\任泰\P11102-110年度本市河川設施檢修改善、零星排水等工程委託監造工作(北區)(111年續約)\11-111年度西區水利建造物預約維護檢修改善工程\11-工程資料\05-估驗資料\第1次\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="3210" yWindow="2670" windowWidth="21600" windowHeight="10995"/>
@@ -24,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
   <si>
-    <t>臺北市政府工務局水利工程處</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>工    程    估    驗    計    價    單</t>
@@ -46,7 +44,7 @@
     <t>工程名稱</t>
   </si>
   <si>
-    <t>111年度西區水利建造物檢修改善及災後淤土、樹木復原及設施搶修預約維護工程</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>會計科目</t>
@@ -82,7 +80,7 @@
     <t>契約編號</t>
   </si>
   <si>
-    <t>H-111-03-111040</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>訂約
@@ -251,7 +249,7 @@
     <t>廠商名稱：</t>
   </si>
   <si>
-    <t>逸峰營造有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>累計解繳金額</t>

--- a/construction_template/data/templates_blank/estimate_report.xlsx
+++ b/construction_template/data/templates_blank/estimate_report.xlsx
@@ -4,7 +4,9 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15"/>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
+    </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="3210" yWindow="2670" windowWidth="21600" windowHeight="10995"/>
@@ -22,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>工    程    估    驗    計    價    單</t>
@@ -44,7 +46,7 @@
     <t>工程名稱</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>會計科目</t>
@@ -80,7 +82,7 @@
     <t>契約編號</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>訂約
@@ -249,7 +251,7 @@
     <t>廠商名稱：</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>累計解繳金額</t>
@@ -1916,7 +1918,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/construction_template/data/templates_blank/estimate_report.xlsx
+++ b/construction_template/data/templates_blank/estimate_report.xlsx
@@ -22,277 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>工    程    估    驗    計    價    單</t>
-  </si>
-  <si>
-    <t>保留款百分比：5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-  </si>
-  <si>
-    <t>第1頁，共1頁</t>
-  </si>
-  <si>
-    <t>第 1 次估驗，第 1 次付款</t>
-  </si>
-  <si>
-    <t>工程名稱</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>會計科目</t>
-  </si>
-  <si>
-    <t>70020302</t>
-  </si>
-  <si>
-    <t>預　算　金　額</t>
-  </si>
-  <si>
-    <t>8500000</t>
-  </si>
-  <si>
-    <t>本期核發金額</t>
-  </si>
-  <si>
-    <t>工程編號</t>
-  </si>
-  <si>
-    <t>111 070020302 030 02</t>
-  </si>
-  <si>
-    <t>開 工 日 期</t>
-  </si>
-  <si>
-    <t>訂  約  總  價</t>
-  </si>
-  <si>
-    <t>本期應扣金額</t>
-  </si>
-  <si>
-    <t>契約編號</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>訂約
-工期</t>
-  </si>
-  <si>
-    <t>日曆天270天</t>
-  </si>
-  <si>
-    <t xml:space="preserve">因契約變更增減估計金額 </t>
-  </si>
-  <si>
-    <t>應 增</t>
-  </si>
-  <si>
-    <t>本期實發金額</t>
-  </si>
-  <si>
-    <t>工程地點</t>
-  </si>
-  <si>
-    <t>臺北市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已工作日數 </t>
-  </si>
-  <si>
-    <t>應 減</t>
-  </si>
-  <si>
-    <t>以前核發金額</t>
-  </si>
-  <si>
-    <t>承辦工務所</t>
-  </si>
-  <si>
-    <t>工務科北區工務所</t>
-  </si>
-  <si>
-    <t xml:space="preserve">估驗日期 </t>
-  </si>
-  <si>
-    <t>結果淨(增、減)</t>
-  </si>
-  <si>
-    <t>總計核發金額</t>
-  </si>
-  <si>
-    <t>估                    驗                    詳                    細                    表</t>
-  </si>
-  <si>
-    <t>契 約 價 金 總 額</t>
-  </si>
-  <si>
-    <t>完成百分率</t>
-  </si>
-  <si>
-    <t>估驗計價</t>
-  </si>
-  <si>
-    <t>保留金額(註2)(百分比：5%)</t>
-  </si>
-  <si>
-    <t>核發金額</t>
-  </si>
-  <si>
-    <t>備    註</t>
-  </si>
-  <si>
-    <t>本次</t>
-  </si>
-  <si>
-    <t>累計</t>
-  </si>
-  <si>
-    <t>發包工程費</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <r>
-      <t>合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>計</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>僅合約項</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本
-次
-應
-扣
-金
-額</t>
-  </si>
-  <si>
-    <t>項      目</t>
-  </si>
-  <si>
-    <t>金    額</t>
-  </si>
-  <si>
-    <t>有價
-廢料
-變賣
-收入
-(註3)</t>
-  </si>
-  <si>
-    <t>說  明</t>
-  </si>
-  <si>
-    <t>本單所計價款及完成百分率數量已核對無訛謹此簽認</t>
-  </si>
-  <si>
-    <t>本期解繳金額</t>
-  </si>
-  <si>
-    <t>以前解繳金額</t>
-  </si>
-  <si>
-    <t>廠商名稱：</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>累計解繳金額</t>
-  </si>
-  <si>
-    <t>合      計</t>
-  </si>
-  <si>
-    <t>中華民國       年       月       日</t>
-  </si>
-  <si>
-    <t>專任工程人員：                 (簽章)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">廠 商 編 製 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 監造單位主管</t>
-  </si>
-  <si>
-    <t>工務科審核</t>
-  </si>
-  <si>
-    <t>工務科長</t>
-  </si>
-  <si>
-    <t>會計室審核</t>
-  </si>
-  <si>
-    <t>會計室主任</t>
-  </si>
-  <si>
-    <t>機關首長或其授權人員</t>
-  </si>
-  <si>
-    <t>註：1.如辦理契約變更或工期展延（含不計工期天數），應填寫修正核定後之預定竣工日期。
-    2.「估驗計價」減去「核發金額」所餘之金額填入「保留金額」欄。
-    3.「有價廢料」係指契約詳細表內編列有價廢料變賣收入項目（例如：瀝青混凝土面層刨除回收剩餘價值、舊有建物拆除後剩餘鋼筋變賣等項目）時填寫，如無該項目則無需填列。
-    4.本表核章欄位可由各機關依實際編制情形參酌修改之。</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1919,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
@@ -1942,9 +1672,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="46"/>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
       <c r="D1" s="46"/>
@@ -1963,8 +1691,10 @@
       <c r="Q1" s="47"/>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
-        <v>1</v>
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工    程    估    驗    計    價    單</t>
+        </is>
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
@@ -1987,179 +1717,303 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="53" t="s">
-        <v>2</v>
+      <c r="D3" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保留款百分比：${retentionRate}%</t>
+        </is>
       </c>
       <c r="E3" s="54"/>
       <c r="F3" s="54"/>
-      <c r="G3" s="62" t="s">
-        <v>3</v>
+      <c r="G3" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+</t>
+        </is>
       </c>
       <c r="H3" s="62"/>
       <c r="I3" s="62"/>
       <c r="J3" s="62"/>
       <c r="K3" s="62"/>
       <c r="L3" s="62"/>
-      <c r="M3" s="58" t="s">
-        <v>4</v>
+      <c r="M3" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第${currentPage}頁，共${totalPage}頁</t>
+        </is>
       </c>
       <c r="N3" s="59"/>
-      <c r="O3" s="60" t="s">
-        <v>5</v>
+      <c r="O3" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第 ${estimateNo} 次估驗，第 ${paymentNo} 次付款</t>
+        </is>
       </c>
       <c r="P3" s="61"/>
       <c r="Q3" s="61"/>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
-        <v>6</v>
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程名稱</t>
+        </is>
       </c>
       <c r="B4" s="52"/>
-      <c r="C4" s="63" t="s">
-        <v>7</v>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${project.name}</t>
+        </is>
       </c>
       <c r="D4" s="64"/>
       <c r="E4" s="65"/>
-      <c r="F4" s="149" t="s">
-        <v>8</v>
+      <c r="F4" s="149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">會計科目</t>
+        </is>
       </c>
       <c r="G4" s="150"/>
-      <c r="H4" s="151"/>
+      <c r="H4" s="151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${accountSubject}</t>
+        </is>
+      </c>
       <c r="I4" s="152"/>
       <c r="J4" s="152"/>
       <c r="K4" s="153"/>
-      <c r="L4" s="50" t="s">
-        <v>10</v>
+      <c r="L4" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">預　算　金　額</t>
+        </is>
       </c>
       <c r="M4" s="50"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="50" t="s">
-        <v>12</v>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${budgetAmount}</t>
+        </is>
+      </c>
+      <c r="O4" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本期核發金額</t>
+        </is>
       </c>
       <c r="P4" s="50"/>
-      <c r="Q4" s="5"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${currentIssued}</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="78" t="s">
-        <v>13</v>
+      <c r="A5" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程編號</t>
+        </is>
       </c>
       <c r="B5" s="79"/>
-      <c r="C5" s="89"/>
+      <c r="C5" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${project.code}</t>
+        </is>
+      </c>
       <c r="D5" s="90"/>
       <c r="E5" s="68"/>
-      <c r="F5" s="44" t="s">
-        <v>15</v>
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">開 工 日 期</t>
+        </is>
       </c>
       <c r="G5" s="45"/>
-      <c r="H5" s="154"/>
+      <c r="H5" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${beginAt}</t>
+        </is>
+      </c>
       <c r="I5" s="155"/>
       <c r="J5" s="155"/>
       <c r="K5" s="156"/>
-      <c r="L5" s="66" t="s">
-        <v>16</v>
+      <c r="L5" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">訂  約  總  價</t>
+        </is>
       </c>
       <c r="M5" s="66"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="66" t="s">
-        <v>17</v>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${contractAmount}</t>
+        </is>
+      </c>
+      <c r="O5" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本期應扣金額</t>
+        </is>
       </c>
       <c r="P5" s="66"/>
-      <c r="Q5" s="6"/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${currentDeduct}</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="78" t="s">
-        <v>18</v>
+      <c r="A6" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約編號</t>
+        </is>
       </c>
       <c r="B6" s="79"/>
-      <c r="C6" s="89" t="s">
-        <v>19</v>
+      <c r="C6" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${project.constructionNo}</t>
+        </is>
       </c>
       <c r="D6" s="90"/>
       <c r="E6" s="68"/>
       <c r="F6" s="72"/>
       <c r="G6" s="73"/>
       <c r="H6" s="74"/>
-      <c r="I6" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>21</v>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">訂約
+工期</t>
+        </is>
+      </c>
+      <c r="J6" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${contractDuration}</t>
+        </is>
       </c>
       <c r="K6" s="68"/>
-      <c r="L6" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="66" t="s">
-        <v>24</v>
+      <c r="L6" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">因契約變更增減估計金額 </t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">應 增</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${changeIncrease}</t>
+        </is>
+      </c>
+      <c r="O6" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本期實發金額</t>
+        </is>
       </c>
       <c r="P6" s="66"/>
-      <c r="Q6" s="6"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${currentNet}</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
-        <v>25</v>
+      <c r="A7" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程地點</t>
+        </is>
       </c>
       <c r="B7" s="79"/>
-      <c r="C7" s="91" t="s">
-        <v>26</v>
+      <c r="C7" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${location}</t>
+        </is>
       </c>
       <c r="D7" s="90"/>
       <c r="E7" s="68"/>
-      <c r="F7" s="157" t="s">
-        <v>27</v>
+      <c r="F7" s="157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已工作日數 </t>
+        </is>
       </c>
       <c r="G7" s="158"/>
-      <c r="H7" s="55"/>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${workedDays}</t>
+        </is>
+      </c>
       <c r="I7" s="56"/>
       <c r="J7" s="56"/>
       <c r="K7" s="57"/>
       <c r="L7" s="70"/>
-      <c r="M7" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="66" t="s">
-        <v>29</v>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">應 減</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${changeDecrease}</t>
+        </is>
+      </c>
+      <c r="O7" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以前核發金額</t>
+        </is>
       </c>
       <c r="P7" s="66"/>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${previousIssued}</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="92" t="s">
-        <v>30</v>
+      <c r="A8" s="92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">承辦工務所</t>
+        </is>
       </c>
       <c r="B8" s="93"/>
-      <c r="C8" s="146" t="s">
-        <v>31</v>
+      <c r="C8" s="146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${officeName}</t>
+        </is>
       </c>
       <c r="D8" s="147"/>
       <c r="E8" s="148"/>
-      <c r="F8" s="159" t="s">
-        <v>32</v>
+      <c r="F8" s="159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">估驗日期 </t>
+        </is>
       </c>
       <c r="G8" s="160"/>
-      <c r="H8" s="75"/>
+      <c r="H8" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${estimateDate}</t>
+        </is>
+      </c>
       <c r="I8" s="76"/>
       <c r="J8" s="76"/>
       <c r="K8" s="77"/>
       <c r="L8" s="71"/>
-      <c r="M8" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="80" t="s">
-        <v>34</v>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">結果淨(增、減)</t>
+        </is>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${changeNet}</t>
+        </is>
+      </c>
+      <c r="O8" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">總計核發金額</t>
+        </is>
       </c>
       <c r="P8" s="80"/>
-      <c r="Q8" s="9"/>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${totalIssued}</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="161" t="s">
-        <v>35</v>
+      <c r="A9" s="161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">估                    驗                    詳                    細                    表</t>
+        </is>
       </c>
       <c r="B9" s="162"/>
       <c r="C9" s="162"/>
@@ -2179,34 +2033,46 @@
       <c r="Q9" s="163"/>
     </row>
     <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="81" t="s">
-        <v>36</v>
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契 約 價 金 總 額</t>
+        </is>
       </c>
       <c r="B10" s="82"/>
       <c r="C10" s="82"/>
       <c r="D10" s="83"/>
       <c r="E10" s="84"/>
-      <c r="F10" s="33" t="s">
-        <v>37</v>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完成百分率</t>
+        </is>
       </c>
       <c r="G10" s="33"/>
-      <c r="H10" s="33" t="s">
-        <v>38</v>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">估驗計價</t>
+        </is>
       </c>
       <c r="I10" s="33"/>
       <c r="J10" s="33"/>
       <c r="K10" s="33"/>
-      <c r="L10" s="44" t="s">
-        <v>39</v>
+      <c r="L10" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保留金額(註2)(百分比：${retentionRate}%)</t>
+        </is>
       </c>
       <c r="M10" s="45"/>
-      <c r="N10" s="33" t="s">
-        <v>40</v>
+      <c r="N10" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">核發金額</t>
+        </is>
       </c>
       <c r="O10" s="33"/>
       <c r="P10" s="33"/>
-      <c r="Q10" s="32" t="s">
-        <v>41</v>
+      <c r="Q10" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">備    註</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2215,449 +2081,449 @@
       <c r="C11" s="86"/>
       <c r="D11" s="87"/>
       <c r="E11" s="88"/>
-      <c r="F11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>42</v>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">累計</t>
+        </is>
+      </c>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次</t>
+        </is>
       </c>
       <c r="I11" s="33"/>
-      <c r="J11" s="33" t="s">
-        <v>43</v>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">累計</t>
+        </is>
       </c>
       <c r="K11" s="33"/>
-      <c r="L11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="N11" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="O11" s="33" t="s">
-        <v>43</v>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">累計</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次</t>
+        </is>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">累計</t>
+        </is>
       </c>
       <c r="P11" s="33"/>
       <c r="Q11" s="32"/>
     </row>
     <row r="12" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>44</v>
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.name}</t>
+        </is>
       </c>
       <c r="B12" s="41"/>
       <c r="C12" s="41"/>
-      <c r="D12" s="43"/>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.contractAmount}</t>
+        </is>
+      </c>
       <c r="E12" s="43"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="34"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.donePercent}</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.totalPercent}</t>
+        </is>
+      </c>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.currentAmount}</t>
+        </is>
+      </c>
       <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
+      <c r="J12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.totalAmount}</t>
+        </is>
+      </c>
       <c r="K12" s="34"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="34"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.currentRetention}</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.totalRetention}</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.currentIssued}</t>
+        </is>
+      </c>
+      <c r="O12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:categories.totalIssued}</t>
+        </is>
+      </c>
       <c r="P12" s="34"/>
-      <c r="Q12" s="35" t="s">
-        <v>45</v>
-      </c>
+      <c r="Q12" s="35"/>
     </row>
-    <row r="13" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="35"/>
+    <row r="13" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合 計(僅合約項)</t>
+        </is>
+      </c>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${totalContractAmount}</t>
+        </is>
+      </c>
+      <c r="E13" s="42"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${totalCurrentAmount}</t>
+        </is>
+      </c>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${totalCumulativeAmount}</t>
+        </is>
+      </c>
+      <c r="K13" s="96"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${totalIssuedAmount}</t>
+        </is>
+      </c>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="37"/>
     </row>
     <row r="14" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="35"/>
+      <c r="A14" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本
+次
+應
+扣
+金
+額</t>
+        </is>
+      </c>
+      <c r="B14" s="117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">項      目</t>
+        </is>
+      </c>
+      <c r="C14" s="118"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金    額</t>
+        </is>
+      </c>
+      <c r="F14" s="167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有價
+廢料
+變賣
+收入
+(註3)</t>
+        </is>
+      </c>
+      <c r="G14" s="129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">說  明</t>
+        </is>
+      </c>
+      <c r="H14" s="130"/>
+      <c r="I14" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金    額</t>
+        </is>
+      </c>
+      <c r="J14" s="95"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本單所計價款及完成百分率數量已核對無訛謹此簽認</t>
+        </is>
+      </c>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="35"/>
+      <c r="A15" s="166"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本期解繳金額</t>
+        </is>
+      </c>
+      <c r="H15" s="45"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="34"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="35"/>
+      <c r="A16" s="166"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以前解繳金額</t>
+        </is>
+      </c>
+      <c r="H16" s="45"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="145"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">廠商名稱：</t>
+        </is>
+      </c>
+      <c r="M16" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${contractorName}</t>
+        </is>
+      </c>
+      <c r="N16" s="101"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="102"/>
     </row>
     <row r="17" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="35"/>
+      <c r="A17" s="166"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">累計解繳金額</t>
+        </is>
+      </c>
+      <c r="H17" s="141"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="22"/>
     </row>
     <row r="18" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="40"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="36"/>
+      <c r="A18" s="166"/>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合      計</t>
+        </is>
+      </c>
+      <c r="C18" s="164"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中華民國       年       月       日</t>
+        </is>
+      </c>
+      <c r="J18" s="131"/>
+      <c r="K18" s="131"/>
+      <c r="L18" s="131"/>
+      <c r="M18" s="131"/>
+      <c r="N18" s="126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">專任工程人員：                 (簽章)</t>
+        </is>
+      </c>
+      <c r="O18" s="127"/>
+      <c r="P18" s="127"/>
+      <c r="Q18" s="128"/>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="37"/>
+    <row r="19" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">廠 商 編 製 </t>
+        </is>
+      </c>
+      <c r="B19" s="113"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 監造單位主管</t>
+        </is>
+      </c>
+      <c r="E19" s="115"/>
+      <c r="F19" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工務科審核</t>
+        </is>
+      </c>
+      <c r="G19" s="116"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工務科長</t>
+        </is>
+      </c>
+      <c r="J19" s="116"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">會計室審核</t>
+        </is>
+      </c>
+      <c r="M19" s="45"/>
+      <c r="N19" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">會計室主任</t>
+        </is>
+      </c>
+      <c r="O19" s="138"/>
+      <c r="P19" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機關首長或其授權人員</t>
+        </is>
+      </c>
+      <c r="Q19" s="132"/>
     </row>
-    <row r="20" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="165" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="117" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="167" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="129" t="s">
-        <v>52</v>
-      </c>
-      <c r="H20" s="130"/>
-      <c r="I20" s="94" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" s="95"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="19"/>
+    <row r="20" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="103"/>
+      <c r="B20" s="104"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="133"/>
+      <c r="Q20" s="134"/>
     </row>
-    <row r="21" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="166"/>
-      <c r="B21" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="90"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="168"/>
-      <c r="G21" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="H21" s="45"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="145"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="21"/>
+    <row r="21" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="106"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="124"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="135"/>
+      <c r="N21" s="135"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="135"/>
+      <c r="Q21" s="134"/>
     </row>
-    <row r="22" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="166"/>
-      <c r="B22" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="90"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="168"/>
-      <c r="G22" s="97" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="45"/>
-      <c r="I22" s="144"/>
-      <c r="J22" s="145"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22" s="100" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" s="101"/>
-      <c r="O22" s="101"/>
-      <c r="P22" s="101"/>
-      <c r="Q22" s="102"/>
+    <row r="22" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="109"/>
+      <c r="B22" s="110"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="136"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="136"/>
+      <c r="Q22" s="137"/>
     </row>
-    <row r="23" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="166"/>
-      <c r="B23" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="140" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="141"/>
-      <c r="I23" s="98">
-        <f>SUM(I21:J22)</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="99"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="22"/>
-    </row>
-    <row r="24" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="166"/>
-      <c r="B24" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="164"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="30">
-        <f>SUM(E21:E23)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="131" t="s">
-        <v>60</v>
-      </c>
-      <c r="J24" s="131"/>
-      <c r="K24" s="131"/>
-      <c r="L24" s="131"/>
-      <c r="M24" s="131"/>
-      <c r="N24" s="126" t="s">
-        <v>61</v>
-      </c>
-      <c r="O24" s="127"/>
-      <c r="P24" s="127"/>
-      <c r="Q24" s="128"/>
-    </row>
-    <row r="25" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="112" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="113"/>
-      <c r="C25" s="114"/>
-      <c r="D25" s="97" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="115"/>
-      <c r="F25" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="116"/>
-      <c r="H25" s="115"/>
-      <c r="I25" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" s="116"/>
-      <c r="K25" s="115"/>
-      <c r="L25" s="97" t="s">
-        <v>66</v>
-      </c>
-      <c r="M25" s="45"/>
-      <c r="N25" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="O25" s="138"/>
-      <c r="P25" s="97" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q25" s="132"/>
-    </row>
-    <row r="26" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="103"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="139"/>
-      <c r="O26" s="135"/>
-      <c r="P26" s="133"/>
-      <c r="Q26" s="134"/>
-    </row>
-    <row r="27" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="106"/>
-      <c r="B27" s="107"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="108"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="108"/>
-      <c r="L27" s="135"/>
-      <c r="M27" s="135"/>
-      <c r="N27" s="135"/>
-      <c r="O27" s="135"/>
-      <c r="P27" s="135"/>
-      <c r="Q27" s="134"/>
-    </row>
-    <row r="28" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="109"/>
-      <c r="B28" s="110"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="122"/>
-      <c r="E28" s="122"/>
-      <c r="F28" s="125"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="136"/>
-      <c r="N28" s="136"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="136"/>
-      <c r="Q28" s="137"/>
-    </row>
-    <row r="29" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="142" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="143"/>
-      <c r="C29" s="143"/>
-      <c r="D29" s="143"/>
-      <c r="E29" s="143"/>
-      <c r="F29" s="143"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="143"/>
-      <c r="I29" s="143"/>
-      <c r="J29" s="143"/>
-      <c r="K29" s="143"/>
-      <c r="L29" s="143"/>
-      <c r="M29" s="143"/>
-      <c r="N29" s="143"/>
-      <c r="O29" s="143"/>
-      <c r="P29" s="143"/>
-      <c r="Q29" s="143"/>
+    <row r="23" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">註：1.如辦理契約變更或工期展延（含不計工期天數），應填寫修正核定後之預定竣工日期。
+    2.「估驗計價」減去「核發金額」所餘之金額填入「保留金額」欄。
+    3.「有價廢料」係指契約詳細表內編列有價廢料變賣收入項目（例如：瀝青混凝土面層刨除回收剩餘價值、舊有建物拆除後剩餘鋼筋變賣等項目）時填寫，如無該項目則無需填列。
+    4.本表核章欄位可由各機關依實際編制情形參酌修改之。</t>
+        </is>
+      </c>
+      <c r="B23" s="143"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="143"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="143"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="143"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="143"/>
+      <c r="N23" s="143"/>
+      <c r="O23" s="143"/>
+      <c r="P23" s="143"/>
+      <c r="Q23" s="143"/>
     </row>
   </sheetData>
   <sheetProtection password="9BD4" sheet="1"/>
-  <mergeCells count="118">
-    <mergeCell ref="A29:Q29"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
+  <mergeCells count="88">
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:K4"/>
@@ -2665,58 +2531,42 @@
     <mergeCell ref="H5:K5"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="J13:K13"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A9:Q9"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="J12:K12"/>
-    <mergeCell ref="I26:K28"/>
-    <mergeCell ref="N24:Q24"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I24:M24"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="P26:Q28"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="L26:M28"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="N26:O28"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A26:C28"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="D26:E28"/>
-    <mergeCell ref="F26:H28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="F20:F23"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="I20:K22"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I18:M18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q22"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="L20:M22"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="N20:O22"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A20:C22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="D20:E22"/>
+    <mergeCell ref="F20:H22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="A7:B7"/>
@@ -2744,35 +2594,21 @@
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A13:C13"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:K10"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="O11:P11"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="A10:E11"/>
     <mergeCell ref="N10:P10"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D18:E18"/>
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="J11:K11"/>
     <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:Q19"/>
+    <mergeCell ref="Q12:Q13"/>
     <mergeCell ref="O13:P13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O15:P15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
